--- a/data/industry/CFM/USB2.xlsx
+++ b/data/industry/CFM/USB2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF35448E-BB0F-4752-B501-EA4EBA9C0465}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A43B1E8-0B47-4AC7-95C9-CC85D6CE22D9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8355" yWindow="2640" windowWidth="27645" windowHeight="16680" firstSheet="1" activeTab="5" xr2:uid="{AA42EAAC-C0FD-2F4D-ACC2-8D822710358F}"/>
+    <workbookView xWindow="8355" yWindow="2640" windowWidth="27645" windowHeight="16680" tabRatio="638" xr2:uid="{AA42EAAC-C0FD-2F4D-ACC2-8D822710358F}"/>
   </bookViews>
   <sheets>
     <sheet name="USB2.0(PCBA) 16GB" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0790C6AE-167D-8C4D-A648-AFDDBAEFC9AE}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="11" bestFit="1" customWidth="1"/>
@@ -3516,6 +3516,581 @@
         <v>1.8</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F126" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G126" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F127" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G127" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F128" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G128" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F129" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G129" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F130" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G130" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F131" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G131" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F132" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G132" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F133" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G133" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F134" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G134" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F135" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G135" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F136" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G136" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F137" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G137" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F138" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G138" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F139" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G139" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F140" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G140" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F141" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G141" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F142" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G142" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F143" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G143" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F144" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G144" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F145" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G145" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F146" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G146" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="F147" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="G147" s="14">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="14">
+        <v>2</v>
+      </c>
+      <c r="F148" s="14">
+        <v>2</v>
+      </c>
+      <c r="G148" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="14">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="F149" s="14">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="G149" s="14">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="14">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="F150" s="14">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="G150" s="14">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3524,7 +4099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AECDF85-3903-FD4D-A061-1D0B2141B871}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="11" bestFit="1" customWidth="1"/>
@@ -6534,6 +7109,581 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F126" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G126" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F127" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G127" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F128" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G128" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F129" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G129" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F130" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G130" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F131" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G131" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F132" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G132" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F133" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G133" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F134" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G134" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F135" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G135" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F136" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G136" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F137" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G137" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F138" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G138" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F139" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G139" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F140" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G140" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F141" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G141" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F142" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G142" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F143" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G143" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F144" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G144" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F145" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G145" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F146" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G146" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F147" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G147" s="9">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="9">
+        <v>2.6</v>
+      </c>
+      <c r="F148" s="9">
+        <v>2.6</v>
+      </c>
+      <c r="G148" s="9">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F149" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G149" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F150" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G150" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6542,7 +7692,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33417336-232C-D148-955A-44D904E50B4B}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="11" bestFit="1" customWidth="1"/>
@@ -9552,6 +10702,581 @@
         <v>2.9</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F126" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G126" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F127" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G127" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F128" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G128" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F129" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G129" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F130" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G130" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F131" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G131" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F132" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G132" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F133" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G133" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F134" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G134" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F135" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G135" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F136" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G136" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F137" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G137" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F138" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G138" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F139" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G139" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F140" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G140" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F141" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G141" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F142" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G142" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F143" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G143" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F144" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G144" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F145" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G145" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F146" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G146" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="F147" s="9">
+        <v>2.9</v>
+      </c>
+      <c r="G147" s="9">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="F148" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="G148" s="9">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="F149" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="G149" s="9">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="F150" s="9">
+        <v>3.6</v>
+      </c>
+      <c r="G150" s="9">
+        <v>3.6</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9560,7 +11285,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7011B464-22BD-9947-893E-8CA0824CF515}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="11" bestFit="1" customWidth="1"/>
@@ -12570,6 +14295,581 @@
         <v>1.78</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F126" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G126" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F127" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G127" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F128" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G128" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F129" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G129" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F130" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G130" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F131" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G131" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F132" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G132" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F133" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G133" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F134" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G134" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F135" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G135" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F136" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G136" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F137" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G137" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F138" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G138" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F139" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G139" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F140" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G140" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F141" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G141" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F142" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G142" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F143" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G143" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F144" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G144" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F145" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G145" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F146" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G146" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="F147" s="9">
+        <v>1.78</v>
+      </c>
+      <c r="G147" s="9">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="9">
+        <v>1.97</v>
+      </c>
+      <c r="F148" s="9">
+        <v>1.97</v>
+      </c>
+      <c r="G148" s="9">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="9">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="F149" s="9">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="G149" s="9">
+        <v>2.0299999999999998</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="9">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="F150" s="9">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="G150" s="9">
+        <v>2.0299999999999998</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12578,7 +14878,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17268ABC-6343-D54D-96AD-0FA1177ACCF3}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="11" bestFit="1" customWidth="1"/>
@@ -15588,6 +17888,581 @@
         <v>2.25</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F126" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G126" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F127" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G127" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F128" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G128" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F129" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G129" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F130" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G130" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F131" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G131" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F132" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G132" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F133" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G133" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F134" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G134" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F135" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G135" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F136" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G136" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F137" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G137" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F138" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G138" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F139" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G139" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F140" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G140" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F141" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G141" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F142" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G142" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F143" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G143" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F144" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G144" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F145" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G145" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F146" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G146" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="F147" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="G147" s="9">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="F148" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="G148" s="9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="9">
+        <v>2.75</v>
+      </c>
+      <c r="F149" s="9">
+        <v>2.75</v>
+      </c>
+      <c r="G149" s="9">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="9">
+        <v>2.75</v>
+      </c>
+      <c r="F150" s="9">
+        <v>2.75</v>
+      </c>
+      <c r="G150" s="9">
+        <v>2.75</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15596,7 +18471,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE0ED5A-51B9-F647-ADB3-8D4BB4D8B720}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="11" bestFit="1" customWidth="1"/>
@@ -18606,6 +21481,581 @@
         <v>2.8</v>
       </c>
     </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="B126" s="11">
+        <v>46050</v>
+      </c>
+      <c r="C126" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F126" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G126" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="B127" s="11">
+        <v>46051</v>
+      </c>
+      <c r="C127" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F127" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G127" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="B128" s="11">
+        <v>46052</v>
+      </c>
+      <c r="C128" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F128" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G128" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="B129" s="11">
+        <v>46055</v>
+      </c>
+      <c r="C129" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F129" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G129" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="B130" s="11">
+        <v>46056</v>
+      </c>
+      <c r="C130" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F130" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G130" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="B131" s="11">
+        <v>46057</v>
+      </c>
+      <c r="C131" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F131" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G131" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="B132" s="11">
+        <v>46058</v>
+      </c>
+      <c r="C132" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F132" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G132" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="B133" s="11">
+        <v>46059</v>
+      </c>
+      <c r="C133" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F133" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G133" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="B134" s="11">
+        <v>46062</v>
+      </c>
+      <c r="C134" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F134" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G134" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="B135" s="11">
+        <v>46063</v>
+      </c>
+      <c r="C135" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F135" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G135" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="B136" s="11">
+        <v>46064</v>
+      </c>
+      <c r="C136" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F136" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G136" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="B137" s="11">
+        <v>46065</v>
+      </c>
+      <c r="C137" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F137" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G137" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="B138" s="11">
+        <v>46066</v>
+      </c>
+      <c r="C138" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F138" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G138" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="B139" s="11">
+        <v>46067</v>
+      </c>
+      <c r="C139" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F139" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G139" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="B140" s="11">
+        <v>46077</v>
+      </c>
+      <c r="C140" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F140" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G140" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B141" s="11">
+        <v>46078</v>
+      </c>
+      <c r="C141" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F141" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G141" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B142" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C142" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F142" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G142" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B143" s="11">
+        <v>46080</v>
+      </c>
+      <c r="C143" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F143" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G143" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B144" s="11">
+        <v>46083</v>
+      </c>
+      <c r="C144" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F144" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G144" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="B145" s="11">
+        <v>46084</v>
+      </c>
+      <c r="C145" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F145" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G145" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="B146" s="11">
+        <v>46085</v>
+      </c>
+      <c r="C146" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F146" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G146" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="B147" s="11">
+        <v>46086</v>
+      </c>
+      <c r="C147" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="F147" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="G147" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B148" s="11">
+        <v>46087</v>
+      </c>
+      <c r="C148" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="F148" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="G148" s="9">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B149" s="11">
+        <v>46090</v>
+      </c>
+      <c r="C149" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="F149" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="G149" s="9">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B150" s="11">
+        <v>46091</v>
+      </c>
+      <c r="C150" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="F150" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="G150" s="9">
+        <v>3.5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
